--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="522">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-10-31</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -878,6 +878,9 @@
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.value</t>
+  </si>
+  <si>
+    <t>保険者番号。英数字 券面記載の保険者番号。</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.period</t>
@@ -6287,7 +6290,7 @@
         <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6366,7 +6369,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>230</v>
@@ -6478,7 +6481,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>238</v>
@@ -6592,10 +6595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6618,70 +6621,70 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="R41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6696,24 +6699,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6739,16 +6742,16 @@
         <v>203</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6773,13 +6776,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6797,7 +6800,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6812,24 +6815,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>184</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6855,16 +6858,16 @@
         <v>180</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6913,7 +6916,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6928,13 +6931,13 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6942,10 +6945,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6971,16 +6974,16 @@
         <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7029,7 +7032,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7047,7 +7050,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7058,10 +7061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7084,19 +7087,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7145,7 +7148,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7154,19 +7157,19 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7174,10 +7177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7203,10 +7206,10 @@
         <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7286,10 +7289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7315,10 +7318,10 @@
         <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>164</v>
@@ -7362,7 +7365,7 @@
         <v>136</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7400,10 +7403,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7429,13 +7432,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7464,10 +7467,10 @@
         <v>196</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7485,7 +7488,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7494,19 +7497,19 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7514,10 +7517,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7543,16 +7546,16 @@
         <v>180</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7601,7 +7604,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7616,10 +7619,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>229</v>
@@ -7630,10 +7633,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7659,16 +7662,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7696,10 +7699,10 @@
         <v>196</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7717,7 +7720,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7732,13 +7735,13 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7746,10 +7749,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7772,16 +7775,16 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7831,7 +7834,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7860,10 +7863,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7889,13 +7892,13 @@
         <v>231</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7945,7 +7948,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7963,7 +7966,7 @@
         <v>131</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>237</v>
@@ -7974,10 +7977,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8000,19 +8003,19 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8061,7 +8064,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8070,19 +8073,19 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8090,10 +8093,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8202,10 +8205,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8316,10 +8319,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8345,16 +8348,16 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8382,10 +8385,10 @@
         <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8403,7 +8406,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8418,13 +8421,13 @@
         <v>200</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8432,10 +8435,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8461,13 +8464,13 @@
         <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8496,10 +8499,10 @@
         <v>196</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8517,7 +8520,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8532,10 +8535,10 @@
         <v>200</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8546,10 +8549,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8575,16 +8578,16 @@
         <v>180</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8633,7 +8636,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8648,10 +8651,10 @@
         <v>200</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8662,10 +8665,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8691,13 +8694,13 @@
         <v>180</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8747,7 +8750,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8762,13 +8765,13 @@
         <v>200</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8776,14 +8779,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8805,13 +8808,13 @@
         <v>180</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8861,7 +8864,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8876,13 +8879,13 @@
         <v>200</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8890,14 +8893,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8919,13 +8922,13 @@
         <v>180</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8975,7 +8978,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8990,10 +8993,10 @@
         <v>200</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9004,14 +9007,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9033,13 +9036,13 @@
         <v>180</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9089,7 +9092,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9104,13 +9107,13 @@
         <v>200</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9118,14 +9121,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9147,13 +9150,13 @@
         <v>180</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9203,7 +9206,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9218,13 +9221,13 @@
         <v>200</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9232,10 +9235,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9261,13 +9264,13 @@
         <v>180</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9317,7 +9320,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9332,13 +9335,13 @@
         <v>200</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9346,10 +9349,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9375,16 +9378,16 @@
         <v>231</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9433,7 +9436,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9448,10 +9451,10 @@
         <v>200</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>237</v>
@@ -9462,10 +9465,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9491,16 +9494,16 @@
         <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9549,7 +9552,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9564,10 +9567,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>184</v>
@@ -9578,10 +9581,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9604,19 +9607,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9665,7 +9668,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9683,7 +9686,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9694,10 +9697,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9723,10 +9726,10 @@
         <v>180</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9806,10 +9809,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9835,10 +9838,10 @@
         <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>164</v>
@@ -9920,14 +9923,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9949,10 +9952,10 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>164</v>
@@ -10007,7 +10010,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10036,10 +10039,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10065,14 +10068,14 @@
         <v>203</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10100,10 +10103,10 @@
         <v>208</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10121,7 +10124,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10139,7 +10142,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10150,10 +10153,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10176,19 +10179,19 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10237,7 +10240,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10252,13 +10255,13 @@
         <v>200</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10266,10 +10269,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10292,17 +10295,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10351,7 +10354,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10366,10 +10369,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10380,10 +10383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10406,17 +10409,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10465,7 +10468,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10480,10 +10483,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10494,10 +10497,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10520,19 +10523,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10581,7 +10584,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -514,7 +514,7 @@
   </si>
   <si>
     <t>医療機関コード（７桁）。Identifier型の拡張「InsuranceOrganizationNo」を使用する。  
-systemには医療機関コードを表すOID「1.2.392.100495.20.3.23」を指定する。  
+systemには医療機関コードを表すOID「http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicalOrganizationID」を指定する。  
 valueには下記の値を格納する。  
 　- 保険医療機関・保険薬局 : `医療機関コード（７桁）`  
 　- 非保険の特定健診・特定保健指導機関 : `機関コード（７桁）`  
@@ -856,7 +856,7 @@
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
-system要素には保険者番号を示すOID"urn:oid:1.2.392.100495.20.3.61"を指定する。</t>
+system要素には保険者番号を示すOID" http://jpfhir.jp/fhir/core/mhlw/IdSystem/InsurerNumber"を指定する。</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.id</t>
@@ -874,7 +874,7 @@
     <t>Organization.identifier:insurerNumber.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.61</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/InsurerNumber</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -856,7 +856,7 @@
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
-system要素には保険者番号を示すOID" http://jpfhir.jp/fhir/core/mhlw/IdSystem/InsurerNumber"を指定する。</t>
+system要素には保険者番号を示す"http://jpfhir.jp/fhir/core/mhlw/IdSystem/InsurerNumber"を指定する。</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber.id</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}org-1:「組織は少なくとも名前または識別子を持つ必要があり、おそらく1つ以上のものもあるかもしれません」 {(identifier.count() + name.count()) &gt; 0}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}org-1:組織は少なくとも名前またはidentifierを持つ必要があり、おそらく1つ以上のものもあるかもしれません {(identifier.count() + name.count()) &gt; 0}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -294,10 +294,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -310,10 +310,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -333,7 +333,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -349,10 +349,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -361,7 +361,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -381,10 +381,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -407,13 +407,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -446,7 +446,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>
@@ -474,7 +474,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -532,7 +532,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -623,22 +623,22 @@
     <t>Organization.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -647,7 +647,7 @@
     <t>Identifier.use</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -661,22 +661,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -691,16 +691,16 @@
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -721,10 +721,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -749,7 +749,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -774,10 +774,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -849,10 +849,10 @@
     <t>insurerNumber</t>
   </si>
   <si>
-    <t>「この組織を複数のシステムで識別する」</t>
-  </si>
-  <si>
-    <t>「異なる複数のシステム上で組織を識別するために使用される組織の識別子」</t>
+    <t>この組織を複数のシステムで識別する</t>
+  </si>
+  <si>
+    <t>異なる複数のシステム上で組織を識別するために使用される組織のidentifier</t>
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
@@ -945,7 +945,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「組織を分類するために使用されます。」</t>
+    <t>組織を分類するために使用されます。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
@@ -1051,7 +1051,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>拡張子は常にURLで切り片にされます。</t>
@@ -1069,7 +1069,7 @@
     <t>連絡先の種別をValueSet(ContactPointSystem)より選択する。  　- phone : 電話　- fax : Fax 　- email : 電子メール　- pager : ポケットベル　- url : 電話、ファックス、ポケットベル、または電子メールアドレスではなく、URLとして表される連絡先。これはWebサイト、ブログ、Skype、Twitter、Facebookなどのさまざまな機関または個人の連絡先を対象としている。電子メールアドレスには使用しないこと。　- sms : SMSメッセージの送信に使用できる連絡先（携帯電話、一部の固定電話など）  　- other : 電話、Fax、ポケットベル、または電子メールアドレスではなく、URLとして表現できない連絡先。例：内部メールアドレス。これは、URLとして表現できる連絡先（Skype、Twitter、Facebookなど）には使用しないこと。</t>
   </si>
   <si>
-    <t>「連絡先のための通信フォーム。」</t>
+    <t>連絡先のための通信フォーム。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -1121,7 +1121,7 @@
     <t>work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】homeは使用しないこと。</t>
   </si>
   <si>
-    <t>「接点の目的を特定する。」(Setten no mokuteki wo tokutei suru.)</t>
+    <t>「接点の目的を特定する。」</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -1134,7 +1134,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>「接点の使用。」(Setten no shiyō.)</t>
+    <t>「接点の使用。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
@@ -1159,10 +1159,10 @@
 </t>
   </si>
   <si>
-    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
-  </si>
-  <si>
-    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -1174,10 +1174,10 @@
     <t>Organization.telecom.period</t>
   </si>
   <si>
-    <t>「コンタクトポイントが使用されている時間帯」</t>
-  </si>
-  <si>
-    <t>「接点が使用されていた/現在使用中である時間期間」</t>
+    <t>コンタクトポイントが使用されている時間帯</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1493,7 +1493,7 @@
     <t>住所が使用されていた/されている期間。 期間は時間の範囲を指定する。使用状況はその期間全体に適用されるか、範囲から1つの値が適用される。  期間は、時間間隔（経過時間の測定値）には使用されない。</t>
   </si>
   <si>
-    <t>アドレスを歴史的な文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
+    <t>アドレスを履歴上の文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
   </si>
   <si>
     <t>Address.period</t>
@@ -1555,11 +1555,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1571,7 +1571,7 @@
     <t>"接触の種類" (Sesshoku no shurui)</t>
   </si>
   <si>
-    <t>「連絡先に到達できる目的を示しています。」</t>
+    <t>連絡先に到達できる目的を示しています。</t>
   </si>
   <si>
     <t>Need to distinguish between multiple contact persons.</t>
@@ -1617,7 +1617,7 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>「連絡先詳細（電話、メールなど）連絡先のため」</t>
+    <t>連絡先詳細（電話、メールなど）連絡先のため</t>
   </si>
   <si>
     <t>当該のパーティーと連絡を取るための連絡先情報（例：電話番号やメールアドレス）</t>
@@ -1635,10 +1635,10 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
-    <t>「連絡のための訪問先または郵送先の住所」</t>
-  </si>
-  <si>
-    <t>「連絡先の訪問または郵便送付先」</t>
+    <t>連絡のための訪問先または郵送先の住所</t>
+  </si>
+  <si>
+    <t>連絡先の訪問または郵便送付先</t>
   </si>
   <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
@@ -1994,7 +1994,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -268,8 +268,8 @@
     <t>集団行動の何らかの形での達成を目的として結成された、正式または非公式に認められた人々または組織のグループ。企業、機関、企業、部門、コミュニティグループ、医療実践グループ、支払者/保険者などが含まれる。</t>
   </si>
   <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}org-1:組織は少なくとも名前またはidentifierを持つ必要があり、おそらく1つ以上のものもあるかもしれません {(identifier.count() + name.count()) &gt; 0}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}org-1:「組織は少なくとも名前または識別子を持つ必要があり、おそらく1つ以上のものもあるかもしれません」 {(identifier.count() + name.count()) &gt; 0}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -294,10 +294,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
-  </si>
-  <si>
-    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
+    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
+  </si>
+  <si>
+    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -310,10 +310,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>「リソースに関するメタデータ」</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -333,7 +333,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
+    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -352,7 +352,7 @@
     <t>「リソースコンテンツの言語」</t>
   </si>
   <si>
-    <t>リソースが書かれている基本言語。</t>
+    <t>「リソースが書かれている基本言語。」</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -381,10 +381,10 @@
 </t>
   </si>
   <si>
-    <t>人間の解釈のためのリソースのテキスト要約</t>
-  </si>
-  <si>
-    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
+    <t>「人間の解釈のためのリソースのテキスト要約」</t>
+  </si>
+  <si>
+    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -410,10 +410,10 @@
     <t>「含まれている、インラインのリソース」</t>
   </si>
   <si>
-    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
-  </si>
-  <si>
-    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
+    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
+  </si>
+  <si>
+    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -446,7 +446,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>
@@ -529,10 +529,10 @@
 user content</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
+    <t xml:space="preserve">無視できない拡張機能 </t>
+  </si>
+  <si>
+    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -849,10 +849,10 @@
     <t>insurerNumber</t>
   </si>
   <si>
-    <t>この組織を複数のシステムで識別する</t>
-  </si>
-  <si>
-    <t>異なる複数のシステム上で組織を識別するために使用される組織のidentifier</t>
+    <t>「この組織を複数のシステムで識別する」</t>
+  </si>
+  <si>
+    <t>「異なる複数のシステム上で組織を識別するために使用される組織の識別子」</t>
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
@@ -945,7 +945,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>組織を分類するために使用されます。</t>
+    <t>「組織を分類するために使用されます。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
@@ -1051,7 +1051,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
   </si>
   <si>
     <t>拡張子は常にURLで切り片にされます。</t>
@@ -1069,7 +1069,7 @@
     <t>連絡先の種別をValueSet(ContactPointSystem)より選択する。  　- phone : 電話　- fax : Fax 　- email : 電子メール　- pager : ポケットベル　- url : 電話、ファックス、ポケットベル、または電子メールアドレスではなく、URLとして表される連絡先。これはWebサイト、ブログ、Skype、Twitter、Facebookなどのさまざまな機関または個人の連絡先を対象としている。電子メールアドレスには使用しないこと。　- sms : SMSメッセージの送信に使用できる連絡先（携帯電話、一部の固定電話など）  　- other : 電話、Fax、ポケットベル、または電子メールアドレスではなく、URLとして表現できない連絡先。例：内部メールアドレス。これは、URLとして表現できる連絡先（Skype、Twitter、Facebookなど）には使用しないこと。</t>
   </si>
   <si>
-    <t>連絡先のための通信フォーム。</t>
+    <t>「連絡先のための通信フォーム。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -1159,10 +1159,10 @@
 </t>
   </si>
   <si>
-    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
-  </si>
-  <si>
-    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
+    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
+  </si>
+  <si>
+    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -1174,10 +1174,10 @@
     <t>Organization.telecom.period</t>
   </si>
   <si>
-    <t>コンタクトポイントが使用されている時間帯</t>
-  </si>
-  <si>
-    <t>接点が使用されていた/現在使用中である時間期間</t>
+    <t>「コンタクトポイントが使用されている時間帯」</t>
+  </si>
+  <si>
+    <t>「接点が使用されていた/現在使用中である時間期間」</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1213,7 +1213,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-org-2:組織の住所は「家」として使用することはできません。 (Soshiki no juusho wa "ie" to shite shiyō suru koto wa dekimasen.) {where(use = 'home').empty()}</t>
+org-2:組織の住所は「家」として使用することはできません。  {where(use = 'home').empty()}</t>
   </si>
   <si>
     <t>ORC-23?</t>
@@ -1555,11 +1555,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>認識されなくても無視できない拡張機能</t>
-  </si>
-  <si>
-    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
+    <t>「認識されなくても無視できない拡張機能」</t>
+  </si>
+  <si>
+    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1571,7 +1571,7 @@
     <t>"接触の種類" (Sesshoku no shurui)</t>
   </si>
   <si>
-    <t>連絡先に到達できる目的を示しています。</t>
+    <t>「連絡先に到達できる目的を示しています。」</t>
   </si>
   <si>
     <t>Need to distinguish between multiple contact persons.</t>
@@ -1617,7 +1617,7 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>連絡先詳細（電話、メールなど）連絡先のため</t>
+    <t>「連絡先詳細（電話、メールなど）連絡先のため」</t>
   </si>
   <si>
     <t>当該のパーティーと連絡を取るための連絡先情報（例：電話番号やメールアドレス）</t>
@@ -1635,10 +1635,10 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
-    <t>連絡のための訪問先または郵送先の住所</t>
-  </si>
-  <si>
-    <t>連絡先の訪問または郵便送付先</t>
+    <t>「連絡のための訪問先または郵送先の住所」</t>
+  </si>
+  <si>
+    <t>「連絡先の訪問または郵便送付先」</t>
   </si>
   <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -268,8 +268,8 @@
     <t>集団行動の何らかの形での達成を目的として結成された、正式または非公式に認められた人々または組織のグループ。企業、機関、企業、部門、コミュニティグループ、医療実践グループ、支払者/保険者などが含まれる。</t>
   </si>
   <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}org-1:「組織は少なくとも名前または識別子を持つ必要があり、おそらく1つ以上のものもあるかもしれません」 {(identifier.count() + name.count()) &gt; 0}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}org-1:組織は少なくとも名前またはidentifierを持つ必要があり、おそらく1つ以上のものもあるかもしれません {(identifier.count() + name.count()) &gt; 0}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -294,10 +294,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -310,10 +310,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -333,7 +333,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -349,10 +349,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>リソースコンテンツの言語</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -361,7 +361,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -381,10 +381,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -407,13 +407,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>含まれている、インラインのリソース</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -446,7 +446,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>
@@ -529,10 +529,10 @@
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">無視できない拡張機能 </t>
-  </si>
-  <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -849,10 +849,10 @@
     <t>insurerNumber</t>
   </si>
   <si>
-    <t>「この組織を複数のシステムで識別する」</t>
-  </si>
-  <si>
-    <t>「異なる複数のシステム上で組織を識別するために使用される組織の識別子」</t>
+    <t>この組織を複数のシステムで識別する</t>
+  </si>
+  <si>
+    <t>異なる複数のシステム上で組織を識別するために使用される組織のidentifier</t>
   </si>
   <si>
     <t>健康保険組合などの保険者の保険者番号を表現する際のIdentifier表現に使用する  
@@ -945,7 +945,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「組織を分類するために使用されます。」</t>
+    <t>組織を分類するために使用されます。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
@@ -1051,7 +1051,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>拡張子は常にURLで切り片にされます。</t>
@@ -1069,7 +1069,7 @@
     <t>連絡先の種別をValueSet(ContactPointSystem)より選択する。  　- phone : 電話　- fax : Fax 　- email : 電子メール　- pager : ポケットベル　- url : 電話、ファックス、ポケットベル、または電子メールアドレスではなく、URLとして表される連絡先。これはWebサイト、ブログ、Skype、Twitter、Facebookなどのさまざまな機関または個人の連絡先を対象としている。電子メールアドレスには使用しないこと。　- sms : SMSメッセージの送信に使用できる連絡先（携帯電話、一部の固定電話など）  　- other : 電話、Fax、ポケットベル、または電子メールアドレスではなく、URLとして表現できない連絡先。例：内部メールアドレス。これは、URLとして表現できる連絡先（Skype、Twitter、Facebookなど）には使用しないこと。</t>
   </si>
   <si>
-    <t>「連絡先のための通信フォーム。」</t>
+    <t>連絡先のための通信フォーム。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -1121,7 +1121,7 @@
     <t>work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】homeは使用しないこと。</t>
   </si>
   <si>
-    <t>「接点の目的を特定する。」</t>
+    <t>接点の目的を特定する。</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -1134,7 +1134,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>「接点の使用。」</t>
+    <t>接点の使用。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
@@ -1159,10 +1159,10 @@
 </t>
   </si>
   <si>
-    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
-  </si>
-  <si>
-    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -1174,10 +1174,10 @@
     <t>Organization.telecom.period</t>
   </si>
   <si>
-    <t>「コンタクトポイントが使用されている時間帯」</t>
-  </si>
-  <si>
-    <t>「接点が使用されていた/現在使用中である時間期間」</t>
+    <t>コンタクトポイントが使用されている時間帯</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1213,7 +1213,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-org-2:組織の住所は「家」として使用することはできません。  {where(use = 'home').empty()}</t>
+org-2:組織の住所は「家」として使用することはできません。 {where(use = 'home').empty()}</t>
   </si>
   <si>
     <t>ORC-23?</t>
@@ -1555,11 +1555,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1568,10 +1568,10 @@
     <t>Organization.contact.purpose</t>
   </si>
   <si>
-    <t>"接触の種類" (Sesshoku no shurui)</t>
-  </si>
-  <si>
-    <t>「連絡先に到達できる目的を示しています。」</t>
+    <t>接触の種類</t>
+  </si>
+  <si>
+    <t>連絡先に到達できる目的を示しています。</t>
   </si>
   <si>
     <t>Need to distinguish between multiple contact persons.</t>
@@ -1617,7 +1617,7 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>「連絡先詳細（電話、メールなど）連絡先のため」</t>
+    <t>連絡先詳細（電話、メールなど）連絡先のため</t>
   </si>
   <si>
     <t>当該のパーティーと連絡を取るための連絡先情報（例：電話番号やメールアドレス）</t>
@@ -1635,10 +1635,10 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
-    <t>「連絡のための訪問先または郵送先の住所」</t>
-  </si>
-  <si>
-    <t>「連絡先の訪問または郵便送付先」</t>
+    <t>連絡のための訪問先または郵送先の住所</t>
+  </si>
+  <si>
+    <t>連絡先の訪問または郵便送付先</t>
   </si>
   <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -1593,25 +1593,19 @@
 </t>
   </si>
   <si>
-    <t>人の名前情報、その一部分と使い方</t>
-  </si>
-  <si>
-    <t>識別のための人の名前情報</t>
-  </si>
-  <si>
-    <t>名前が変更されたり、違っていると指摘されたり、コンテキストによって使われる名前が異なる場合がある。名前は、コンテキストに応じて重要性が異なるさまざまなタイプの部分に分割される場合があり、部分への分割は必ずしも重要ではない。個人名の場合、さまざまな部分に暗黙の意味が含まれている場合と含まれていない場合がある。さまざまな文化が名前の部分にさまざまな重要性を関連付けており、システムが世界中の名前の部分を気にする必要がある程度は大きく異なる。</t>
+    <t>コンタクトに関連する名前</t>
+  </si>
+  <si>
+    <t>連絡関係にある名前</t>
   </si>
   <si>
     <t>Need to be able to track the person by name.</t>
   </si>
   <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>ProviderName</t>
+    <t>PID-5, PID-9</t>
+  </si>
+  <si>
+    <t>./name</t>
   </si>
   <si>
     <t>Organization.contact.telecom</t>
@@ -10187,11 +10181,9 @@
       <c r="M72" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10249,19 +10241,19 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AM72" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10269,10 +10261,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10298,14 +10290,14 @@
         <v>314</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10354,7 +10346,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10369,10 +10361,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10383,10 +10375,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10412,14 +10404,14 @@
         <v>374</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10468,7 +10460,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10483,10 +10475,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10497,10 +10489,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10523,19 +10515,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>472</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10584,7 +10576,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -446,7 +446,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>
@@ -6501,7 +6501,7 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>240</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -804,7 +804,7 @@
     <t>福祉医療施設を区別するため医療機関コード（１０桁）を格納するためのIdentifier/Slicing定義。</t>
   </si>
   <si>
-    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no```を使用する。  
+    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode```を使用する。  
 value : ```医療機関コード（１０桁）```を使用する。  
 医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。 </t>
   </si>
@@ -827,7 +827,7 @@
     <t>Organization.identifier:medicalInstitutionCode.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode</t>
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -837,10 +837,6 @@
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Organization.identifier:insurerNumber</t>
@@ -1964,17 +1960,17 @@
   <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.2421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.09765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.0703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1983,26 +1979,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.72265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="187.0625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5469,7 +5465,7 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>240</v>
@@ -5557,13 +5553,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5588,13 +5584,13 @@
         <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>252</v>
@@ -5675,7 +5671,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>179</v>
@@ -5787,7 +5783,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>185</v>
@@ -5901,7 +5897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>191</v>
@@ -6017,7 +6013,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>202</v>
@@ -6133,7 +6129,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>213</v>
@@ -6178,7 +6174,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6249,7 +6245,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>222</v>
@@ -6284,7 +6280,7 @@
         <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6363,7 +6359,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>230</v>
@@ -6475,7 +6471,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>238</v>
@@ -6589,10 +6585,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6615,26 +6611,26 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="O41" t="s" s="2">
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="P41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="R41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6678,7 +6674,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6693,24 +6689,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>288</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6736,16 +6732,16 @@
         <v>203</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6770,14 +6766,14 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6794,7 +6790,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6809,24 +6805,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>184</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6852,16 +6848,16 @@
         <v>180</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6910,7 +6906,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6925,13 +6921,13 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6939,10 +6935,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6968,16 +6964,16 @@
         <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7026,7 +7022,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7044,7 +7040,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7055,10 +7051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7081,19 +7077,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7142,7 +7138,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7151,19 +7147,19 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AJ45" t="s" s="2">
+      <c r="AK45" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AK45" t="s" s="2">
+      <c r="AL45" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7171,10 +7167,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7200,10 +7196,10 @@
         <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7283,10 +7279,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7312,10 +7308,10 @@
         <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>164</v>
@@ -7359,7 +7355,7 @@
         <v>136</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7397,10 +7393,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7426,13 +7422,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7461,28 +7457,28 @@
         <v>196</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7491,19 +7487,19 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7511,10 +7507,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7540,16 +7536,16 @@
         <v>180</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7598,7 +7594,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7613,10 +7609,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>229</v>
@@ -7627,10 +7623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7656,16 +7652,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7693,28 +7689,28 @@
         <v>196</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7729,13 +7725,13 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7743,10 +7739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7769,16 +7765,16 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7828,7 +7824,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7857,10 +7853,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7886,13 +7882,13 @@
         <v>231</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7942,7 +7938,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7960,7 +7956,7 @@
         <v>131</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>237</v>
@@ -7971,10 +7967,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7997,19 +7993,19 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8058,7 +8054,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8067,19 +8063,19 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AJ53" t="s" s="2">
+      <c r="AK53" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AK53" t="s" s="2">
+      <c r="AL53" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8087,10 +8083,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8199,10 +8195,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8313,10 +8309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8342,16 +8338,16 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8379,28 +8375,28 @@
         <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z56" t="s" s="2">
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8415,13 +8411,13 @@
         <v>200</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8429,10 +8425,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8458,13 +8454,13 @@
         <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8493,28 +8489,28 @@
         <v>196</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="Z57" t="s" s="2">
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8529,10 +8525,10 @@
         <v>200</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8543,10 +8539,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8572,16 +8568,16 @@
         <v>180</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8630,7 +8626,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8645,10 +8641,10 @@
         <v>200</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8659,10 +8655,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8688,13 +8684,13 @@
         <v>180</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8744,7 +8740,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8759,13 +8755,13 @@
         <v>200</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8773,14 +8769,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8802,13 +8798,13 @@
         <v>180</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8858,7 +8854,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8873,13 +8869,13 @@
         <v>200</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8887,14 +8883,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8916,13 +8912,13 @@
         <v>180</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8972,7 +8968,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8987,10 +8983,10 @@
         <v>200</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9001,14 +8997,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9030,13 +9026,13 @@
         <v>180</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9086,7 +9082,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9101,13 +9097,13 @@
         <v>200</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9115,14 +9111,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9144,13 +9140,13 @@
         <v>180</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9200,7 +9196,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9215,13 +9211,13 @@
         <v>200</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9229,10 +9225,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9258,13 +9254,13 @@
         <v>180</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9314,7 +9310,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9329,13 +9325,13 @@
         <v>200</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9343,10 +9339,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9372,16 +9368,16 @@
         <v>231</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9430,7 +9426,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9445,10 +9441,10 @@
         <v>200</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>237</v>
@@ -9459,10 +9455,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9488,16 +9484,16 @@
         <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9546,7 +9542,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9561,10 +9557,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>184</v>
@@ -9575,10 +9571,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9601,19 +9597,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9662,7 +9658,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9680,7 +9676,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9691,10 +9687,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9720,10 +9716,10 @@
         <v>180</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9803,10 +9799,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9832,10 +9828,10 @@
         <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>164</v>
@@ -9917,14 +9913,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9946,10 +9942,10 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>164</v>
@@ -10004,7 +10000,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10033,10 +10029,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10062,14 +10058,14 @@
         <v>203</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10097,11 +10093,11 @@
         <v>208</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10118,7 +10114,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10136,7 +10132,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10147,10 +10143,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10173,17 +10169,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10232,7 +10228,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10247,10 +10243,10 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10261,10 +10257,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10287,17 +10283,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10346,7 +10342,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10361,10 +10357,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10375,10 +10371,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10401,17 +10397,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10460,7 +10456,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10475,10 +10471,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10489,10 +10485,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10515,19 +10511,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10576,7 +10572,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -804,7 +804,7 @@
     <t>福祉医療施設を区別するため医療機関コード（１０桁）を格納するためのIdentifier/Slicing定義。</t>
   </si>
   <si>
-    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode```を使用する。  
+    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no```を使用する。  
 value : ```医療機関コード（１０桁）```を使用する。  
 医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。 </t>
   </si>
@@ -827,7 +827,7 @@
     <t>Organization.identifier:medicalInstitutionCode.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no</t>
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -364,7 +364,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -679,7 +679,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -944,7 +944,7 @@
     <t>組織を分類するために使用されます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1576,7 +1576,7 @@
     <t>「連絡を取りたい目的のための連絡先」となります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1643,7 +1643,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-organization.xlsx
@@ -903,7 +903,7 @@
 この要素は修飾子としてラベル付けされています。これは、リソースが誤って作成されたことを示すために使用できるためです。</t>
   </si>
   <si>
-    <t>レコードが使用されなくなったことを示すためのフラグが必要で、一般的にUIではユーザのために非表示にする必要がある。</t>
+    <t>レコードが使用されなくなったことを示すためのフラグが必要で、一般的にUIではユーザーのために非表示にする必要がある。</t>
   </si>
   <si>
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
